--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/DEVBHUMI DWARKA.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/DEVBHUMI DWARKA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-27\ICS\2.0   PLANNING 2026-27\Kharif 2026-27\2.0\2.0 planning 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870B3BB2-0815-43D4-813C-75813D0C1499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0090EC0A-B26A-4736-881C-0E39040DCA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central 2.0" sheetId="1" r:id="rId1"/>
@@ -461,6 +461,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -512,7 +513,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -795,100 +795,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="11"/>
+    <col min="1" max="1" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-    </row>
-    <row r="2" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+    </row>
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-    </row>
-    <row r="3" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-    </row>
-    <row r="4" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="24">
         <v>8</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23" t="s">
+      <c r="E4" s="24"/>
+      <c r="F4" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23">
+      <c r="G4" s="24"/>
+      <c r="H4" s="24">
         <v>6</v>
       </c>
-      <c r="I4" s="23"/>
+      <c r="I4" s="24"/>
       <c r="J4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="27" t="s">
+    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27" t="s">
+      <c r="E5" s="28"/>
+      <c r="F5" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27" t="s">
+      <c r="G5" s="28"/>
+      <c r="H5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="27"/>
+      <c r="I5" s="28"/>
       <c r="J5" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -918,7 +918,7 @@
       </c>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>18</v>
       </c>
@@ -943,7 +943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>19</v>
       </c>
@@ -968,7 +968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>19</v>
       </c>
@@ -997,7 +997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>20</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>23</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
@@ -1066,12 +1066,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
       <c r="D13" s="5">
         <f>SUM(D7:D12)</f>
         <v>8</v>
@@ -1092,25 +1092,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-    </row>
-    <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="14" t="s">
         <v>40</v>
       </c>
       <c r="C15" s="9" t="s">
@@ -1131,11 +1131,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="14" t="s">
         <v>40</v>
       </c>
       <c r="C16" s="9" t="s">
@@ -1156,11 +1156,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="14" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="9" t="s">
@@ -1181,11 +1181,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="14" t="s">
         <v>40</v>
       </c>
       <c r="C18" s="9" t="s">
@@ -1206,11 +1206,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="14" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -1231,7 +1231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="10"/>
@@ -1246,12 +1246,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="25"/>
-      <c r="C21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="27"/>
       <c r="D21" s="5">
         <f>SUM(D15:D19)</f>
         <v>0</v>
@@ -1272,12 +1272,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+    <row r="22" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="27"/>
       <c r="D22" s="5">
         <f>+D13+D21</f>
         <v>8</v>
@@ -1298,19 +1298,19 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1338,99 +1338,99 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-    </row>
-    <row r="2" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+    </row>
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-    </row>
-    <row r="3" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-    </row>
-    <row r="4" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="29" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="24">
         <v>4</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23" t="s">
+      <c r="E4" s="24"/>
+      <c r="F4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23">
+      <c r="G4" s="24"/>
+      <c r="H4" s="24">
         <v>4</v>
       </c>
-      <c r="I4" s="23"/>
+      <c r="I4" s="24"/>
       <c r="J4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="27" t="s">
+    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27" t="s">
+      <c r="E5" s="28"/>
+      <c r="F5" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27" t="s">
+      <c r="G5" s="28"/>
+      <c r="H5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="27"/>
+      <c r="I5" s="28"/>
       <c r="J5" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>20</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>23</v>
       </c>
@@ -1518,12 +1518,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
       <c r="D9" s="5">
         <f>SUM(D7:D8)</f>
         <v>4</v>
@@ -1544,25 +1544,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-    </row>
-    <row r="11" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="14" t="s">
         <v>40</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -1583,11 +1583,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="14" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -1608,12 +1608,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="5">
         <f>SUM(D11:D12)</f>
         <v>0</v>
@@ -1634,12 +1634,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="27"/>
       <c r="D14" s="5">
         <f>+D9+D13</f>
         <v>4</v>
@@ -1660,19 +1660,19 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="16">
